--- a/volumes/02-solar-home-systems/templates/AEF_V2_T07_Borrowing_Base_and_Term_Sheet.xlsx
+++ b/volumes/02-solar-home-systems/templates/AEF_V2_T07_Borrowing_Base_and_Term_Sheet.xlsx
@@ -614,7 +614,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AFRICA ENERGY FINANCE  |  VOLUME 2  |  SOLAR HOME SYSTEMS</t>
+          <t>AFRICA ENERGY FINANCE  |  BOOK 2  |  PAYGO SOLAR FINANCE</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -650,7 +650,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Template T07  |  Version 1.0  |  Author &amp; ideation: Emmanuel Boujieka Kamga</t>
+          <t>Template T07  |  Version 0.9 (pre-release)  |  Author &amp; ideation: Emmanuel Boujieka Kamga</t>
         </is>
       </c>
       <c r="B4" s="6" t="n"/>
@@ -795,7 +795,7 @@
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>Links to the Volume 2 model and book</t>
+          <t>Links to Book 2 and MODEL 2</t>
         </is>
       </c>
       <c r="B22" s="6" t="n"/>
@@ -844,7 +844,7 @@
     <row r="27">
       <c r="A27" s="13" t="inlineStr">
         <is>
-          <t>Decision support material; not investment, legal, tax or accounting advice. Example values are illustrative and refer to the fictional SolaraPay case where data are needed. (c) 2026 Emmanuel Boujieka Kamga.</t>
+          <t>Decision support material; not investment, legal, tax or accounting advice. Example values are illustrative and refer to the book's worked examples or to the fictional SolaraPay case. (c) 2026 Emmanuel Boujieka Kamga.</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;L&amp;"Arial"&amp;8 Africa Energy Finance | Volume 2 Template T07&amp;C&amp;"Arial"&amp;8 &amp;A&amp;R&amp;"Arial"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial"&amp;8 Africa Energy Finance | Book 2 Template T07 | Version 0.9 (pre-release)&amp;C&amp;"Arial"&amp;8 &amp;A&amp;R&amp;"Arial"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -901,7 +901,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AFRICA ENERGY FINANCE  |  VOLUME 2  |  SOLAR HOME SYSTEMS</t>
+          <t>AFRICA ENERGY FINANCE  |  BOOK 2  |  PAYGO SOLAR FINANCE</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -952,7 +952,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Template T07  |  Version 1.0  |  Author &amp; ideation: Emmanuel Boujieka Kamga</t>
+          <t>Template T07  |  Version 0.9 (pre-release)  |  Author &amp; ideation: Emmanuel Boujieka Kamga</t>
         </is>
       </c>
       <c r="B4" s="6" t="n"/>
@@ -1804,7 +1804,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;L&amp;"Arial"&amp;8 Africa Energy Finance | Volume 2 Template T07&amp;C&amp;"Arial"&amp;8 &amp;A&amp;R&amp;"Arial"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial"&amp;8 Africa Energy Finance | Book 2 Template T07 | Version 0.9 (pre-release)&amp;C&amp;"Arial"&amp;8 &amp;A&amp;R&amp;"Arial"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1835,7 +1835,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AFRICA ENERGY FINANCE  |  VOLUME 2  |  SOLAR HOME SYSTEMS</t>
+          <t>AFRICA ENERGY FINANCE  |  BOOK 2  |  PAYGO SOLAR FINANCE</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1877,7 +1877,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Template T07  |  Version 1.0  |  Author &amp; ideation: Emmanuel Boujieka Kamga</t>
+          <t>Template T07  |  Version 0.9 (pre-release)  |  Author &amp; ideation: Emmanuel Boujieka Kamga</t>
         </is>
       </c>
       <c r="B4" s="6" t="n"/>
@@ -2293,7 +2293,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader/>
-    <oddFooter>&amp;L&amp;"Arial"&amp;8 Africa Energy Finance | Volume 2 Template T07&amp;C&amp;"Arial"&amp;8 &amp;A&amp;R&amp;"Arial"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial"&amp;8 Africa Energy Finance | Book 2 Template T07 | Version 0.9 (pre-release)&amp;C&amp;"Arial"&amp;8 &amp;A&amp;R&amp;"Arial"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
